--- a/ksoft_old/docs/records/Finance_Institution_(Portador)_Records.xlsx
+++ b/ksoft_old/docs/records/Finance_Institution_(Portador)_Records.xlsx
@@ -2351,13 +2351,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5508BB72-46A9-4670-B11A-ED8AA7369B91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0384F30E-1B3A-4019-9855-E42D61EA3F0B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B38F3B9A-CA22-494D-98DD-885CC64DFC2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2245326-E612-41E2-8E26-8CBE39833024}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42B955B3-40BD-4CAF-9FD5-963CD519E053}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5624DC50-5414-45BF-8ACB-35A502C5A5B3}"/>
 </file>
--- a/ksoft_old/docs/records/Finance_Institution_(Portador)_Records.xlsx
+++ b/ksoft_old/docs/records/Finance_Institution_(Portador)_Records.xlsx
@@ -2351,13 +2351,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0384F30E-1B3A-4019-9855-E42D61EA3F0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07C6B6D8-9A09-47D0-94DE-537422AD5006}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2245326-E612-41E2-8E26-8CBE39833024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DF2CAB5-80D1-41EA-AA05-532EE50805A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5624DC50-5414-45BF-8ACB-35A502C5A5B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{012E70FA-1238-4EC7-A159-AA760BDF08DF}"/>
 </file>
--- a/ksoft_old/docs/records/Finance_Institution_(Portador)_Records.xlsx
+++ b/ksoft_old/docs/records/Finance_Institution_(Portador)_Records.xlsx
@@ -2351,13 +2351,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07C6B6D8-9A09-47D0-94DE-537422AD5006}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5508BB72-46A9-4670-B11A-ED8AA7369B91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DF2CAB5-80D1-41EA-AA05-532EE50805A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B38F3B9A-CA22-494D-98DD-885CC64DFC2C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{012E70FA-1238-4EC7-A159-AA760BDF08DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42B955B3-40BD-4CAF-9FD5-963CD519E053}"/>
 </file>